--- a/stories/arbres/TREE-EMO-011.xlsx
+++ b/stories/arbres/TREE-EMO-011.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|À la maison, le jeu devient trop fort. Trop de voix. Trop près. Noé sent que c'est trop. Maman est dans le couloir. Papa plie du linge. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1649,6 +1676,11 @@
         <v>12</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|La pomme roule trop vite entre les mains. C'est trop. C'est une pomme. Le sable est un peu frais. Noé s'approche, sans courir. Papa n'est pas loin. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1857,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|C'est trop. Que dit-on ? Avec une pomme.</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2030,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. Noé retient le geste. Il respire.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2221,11 @@
         <v>12</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2388,11 @@
         <v>12</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi la cuisine, après une pomme. Un nuage passe devant le soleil. Près de la cuisine, Noé prend le temps. Pas de course. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2527,6 +2579,11 @@
         <v>12</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2689,6 +2746,11 @@
         <v>12</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint les cubes, après une pomme et la cuisine. La tasse est encore tiède. On dit merci. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. On laisse les cubes à sa place. Noé est près de maman. Le soleil est encore là.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2851,6 +2913,11 @@
         <v>12</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3013,6 +3080,11 @@
         <v>12</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint le livre, après une pomme et la cuisine. Le parquet craque un tout petit peu. On écoute jusqu'au bout. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. On écoute le silence une seconde. Noé est assis. On gardu geste.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3175,6 +3247,11 @@
         <v>12</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3199,7 +3276,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint la dînette, après une pomme et la cuisine. Une abeille bourdonne loin. On attend un petit moment. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. Maman dit : je t'ai entendu. Papa aussi. Papa et maman sont là.</t>
+          <t>Noé rejoint la dînette, après une pomme et la cuisine. Une abeille bourdonne loin. On attend un petit moment. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. Je t'ai entendu. Papa aussi. Papa et maman sont là.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3337,6 +3414,12 @@
         <v>12</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint la dînette, après une pomme et la cuisine. Une abeille bourdonne loin. On attend un petit moment. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman.
+maman|Je t'ai entendu. Papa aussi. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3499,6 +3582,11 @@
         <v>12</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3661,6 +3749,11 @@
         <v>12</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi le jardin, après une pomme. Ça sent le savon de maman. Noé range un peu autour du jardin. Il respire. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3847,6 +3940,11 @@
         <v>12</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4009,6 +4107,11 @@
         <v>12</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint les cubes, après une pomme et le jardin. Un gravier roule sous une semelle. On pose les fesses sur une chaise. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. On laisse les cubes à sa place. Noé est près de maman. On respire.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4171,6 +4274,11 @@
         <v>12</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4333,6 +4441,11 @@
         <v>12</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint le livre, après une pomme et le jardin. La fenêtre tremble un tout petit peu. On sourit un peu. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. On écoute le silence une seconde. Noé est assis. Merci, et au dodo bientôt.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4495,6 +4608,11 @@
         <v>12</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4519,7 +4637,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint la dînette, après une pomme et le jardin. Ça sent le savon de maman. On boit une gorgée d'eau. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. Maman dit : je t'ai entendu. Papa aussi. Le jeu peut recommencer.</t>
+          <t>Noé rejoint la dînette, après une pomme et le jardin. Ça sent le savon de maman. On boit une gorgée d'eau. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. Je t'ai entendu. Papa aussi. Le jeu peut recommencer.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4657,6 +4775,13 @@
         <v>12</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint la dînette, après une pomme et le jardin. Ça sent le savon de maman. On boit une gorgée d'eau. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman.
+maman|Je t'ai entendu. Papa aussi.
+narrateur|Le jeu peut recommencer.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4819,6 +4944,11 @@
         <v>12</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4981,6 +5111,11 @@
         <v>12</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi la chambre, après une pomme. Le lait est tiède. La chambre reste à sa place. Noé aussi. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5167,6 +5302,11 @@
         <v>12</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5329,6 +5469,11 @@
         <v>12</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint les cubes, après une pomme et la chambre. Un pigeon roucoule. On essuie une miette. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. Noé serre la main de maman, tout doux. On se serre un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5491,6 +5636,11 @@
         <v>12</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5653,6 +5803,11 @@
         <v>12</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint le livre, après une pomme et la chambre. La cuillère tinte. On referme un livre. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. Noé nomme encore le mot, tout bas. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5815,6 +5970,11 @@
         <v>12</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5977,6 +6137,11 @@
         <v>12</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint la dînette, après une pomme et la chambre. Le ballon est un peu poudreux. On pose un jouet à sa place. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. Noé pose la dînette et va vers maman. La journée continue, tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6139,6 +6304,11 @@
         <v>12</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6301,6 +6471,11 @@
         <v>12</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Le yaourt manque de tomber. C'est trop. Noé s'occupe de un yaourt. Le soleil chauffe un peu le nez. Maman sourit. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6477,6 +6652,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|C'est trop. Que dit-on ? Avec un yaourt.</t>
         </is>
       </c>
     </row>
@@ -6645,6 +6825,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. Noé répète le mot. Maman hoche la tête.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6831,6 +7016,11 @@
         <v>12</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6993,6 +7183,11 @@
         <v>12</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi la cuisine, après un yaourt. Le train souffle au loin. On continue avec la cuisine. Noé gardu geste sûr. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7179,6 +7374,11 @@
         <v>12</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7341,6 +7541,11 @@
         <v>12</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint les cubes, après un yaourt et la cuisine. Une goutte de pluie sèche déjà. On marche tout doucement. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. On écoute le silence une seconde. Noé est assis. On se dit à plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7503,6 +7708,11 @@
         <v>12</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7527,7 +7737,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint le livre, après un yaourt et la cuisine. Le banc est tiède. On se tait une seconde. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. Maman dit : je t'ai entendu. Papa aussi. Le soleil est encore là.</t>
+          <t>Noé rejoint le livre, après un yaourt et la cuisine. Le banc est tiède. On se tait une seconde. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. Je t'ai entendu. Papa aussi. Le soleil est encore là.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7665,6 +7875,13 @@
         <v>12</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint le livre, après un yaourt et la cuisine. Le banc est tiède. On se tait une seconde. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman.
+maman|Je t'ai entendu. Papa aussi.
+narrateur|Le soleil est encore là.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7827,6 +8044,11 @@
         <v>12</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7989,6 +8211,11 @@
         <v>12</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint la dînette, après un yaourt et la cuisine. Ça sent le savon des mains. On ouvre les mains, loin de l'autre. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. On laisse la dînette à sa place. Noé est près de maman. On gardu geste.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8151,6 +8378,11 @@
         <v>12</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8313,6 +8545,11 @@
         <v>12</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi le jardin, après un yaourt. Le pain croustille. Près du jardin, Noé prend le temps. Pas de course. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8499,6 +8736,11 @@
         <v>12</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8661,6 +8903,11 @@
         <v>12</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint les cubes, après un yaourt et le jardin. Une feuille tourne et tombe. On s'assoit près de l'adulte. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. On écoute le silence une seconde. Noé est assis. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8823,6 +9070,11 @@
         <v>12</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8985,6 +9237,11 @@
         <v>12</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint le livre, après un yaourt et le jardin. L'eau fait un tout petit bruit. On nomme ce qu'on sent. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. Noé pose le livre et va vers maman. On respire.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9147,6 +9404,11 @@
         <v>12</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9309,6 +9571,11 @@
         <v>12</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint la dînette, après un yaourt et le jardin. Le soleil chauffe un peu le nez. On reprend le jeu, plus calme. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. Noé serre la main de maman, tout doux. Merci, et au dodo bientôt.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9471,6 +9738,11 @@
         <v>12</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9633,6 +9905,11 @@
         <v>12</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi la chambre, après un yaourt. Le coussin est moelleux. Près de la chambre, Noé prend le temps. Pas de course. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9819,6 +10096,11 @@
         <v>12</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9981,6 +10263,11 @@
         <v>12</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint les cubes, après un yaourt et la chambre. Une plume vole. On range les chaussures. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. Noé nomme encore le mot, tout bas. Le jeu peut recommencer.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10143,6 +10430,11 @@
         <v>12</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10305,6 +10597,11 @@
         <v>12</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint le livre, après un yaourt et la chambre. Le pain croustille. On met le doudou près de soi. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. Noé pose le livre et va vers maman. On se serre un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10467,6 +10764,11 @@
         <v>12</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10629,6 +10931,11 @@
         <v>12</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint la dînette, après un yaourt et la chambre. La laine du doudou est douce. On écoute le cœur, tout doux. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. Noé serre la main de maman, tout doux. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10791,6 +11098,11 @@
         <v>12</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10953,6 +11265,11 @@
         <v>12</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Le pain passe trop près du visage. C'est trop. Voilà un morceau de pain. Un coq chante une fois. Noé pose les pieds par terre, près de maman. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11129,6 +11446,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|C'est trop. Que dit-on ? Avec un morceau de pain.</t>
         </is>
       </c>
     </row>
@@ -11297,6 +11619,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. Noé pose les pieds par terre. On continue, tout calme.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11483,6 +11810,11 @@
         <v>12</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11645,6 +11977,11 @@
         <v>12</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi la cuisine, après un morceau de pain. La tasse est encore tiède. La cuisine est là. Noé pose les mains à vue, loin de l'autre. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11831,6 +12168,11 @@
         <v>12</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11993,6 +12335,11 @@
         <v>12</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint les cubes, après un morceau de pain et la cuisine. Un galet est lisse dans la main. On secoue les mains, loin. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. Noé nomme encore le mot, tout bas. La journée continue, tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12155,6 +12502,11 @@
         <v>12</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12317,6 +12669,11 @@
         <v>12</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint le livre, après un morceau de pain et la cuisine. Le train souffle au loin. On pose le sac. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. Noé serre la main de maman, tout doux. On se dit à plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12479,6 +12836,11 @@
         <v>12</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12641,6 +13003,11 @@
         <v>12</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint la dînette, après un morceau de pain et la cuisine. Une vache meugle, loin. On dit le mot de l'émotion. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. Noé range la dînette un instant. Puis il reprend, calme. Le soleil est encore là.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12803,6 +13170,11 @@
         <v>12</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12965,6 +13337,11 @@
         <v>12</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi le jardin, après un morceau de pain. Ça sent le pain encore chaud. Noé attend près du jardin. Il ne prend pas de force. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13151,6 +13528,11 @@
         <v>12</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13175,7 +13557,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint les cubes, après un morceau de pain et le jardin. Un grillon chante, tout petit. On invite d'une petite voix. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. Maman dit : je t'ai entendu. Papa aussi. On gardu geste.</t>
+          <t>Noé rejoint les cubes, après un morceau de pain et le jardin. Un grillon chante, tout petit. On invite d'une petite voix. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. Je t'ai entendu. Papa aussi. On gardu geste.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13313,6 +13695,12 @@
         <v>12</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint les cubes, après un morceau de pain et le jardin. Un grillon chante, tout petit. On invite d'une petite voix. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman.
+maman|Je t'ai entendu. Papa aussi. On gardu geste.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13475,6 +13863,11 @@
         <v>12</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13637,6 +14030,11 @@
         <v>12</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint le livre, après un morceau de pain et le jardin. Le bois de la table est lisse. On attend la réponse. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. On écoute le silence une seconde. Noé est assis. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13799,6 +14197,11 @@
         <v>12</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13961,6 +14364,11 @@
         <v>12</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint la dînette, après un morceau de pain et le jardin. Une goutte tombe dans l'évier. On propose une autre idée. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. Noé serre la main de maman, tout doux. On respire.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14123,6 +14531,11 @@
         <v>12</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14285,6 +14698,11 @@
         <v>12</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi la chambre, après un morceau de pain. Un nuage passe devant le soleil. On continue avec la chambre. Noé gardu geste sûr. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14471,6 +14889,11 @@
         <v>12</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14633,6 +15056,11 @@
         <v>12</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint les cubes, après un morceau de pain et la chambre. Le toboggan est un peu froid. On va vers papa ou maman. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. Noé nomme encore le mot, tout bas. Merci, et au dodo bientôt.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14795,6 +15223,11 @@
         <v>12</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14957,6 +15390,11 @@
         <v>12</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint le livre, après un morceau de pain et la chambre. La clochette de la porte tinte. On dit stop, tout clair. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. Noé boit une gorgée. Il se sent plus léger. Le jeu peut recommencer.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15119,6 +15557,11 @@
         <v>12</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15281,6 +15724,11 @@
         <v>12</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint la dînette, après un morceau de pain et la chambre. Ça sent le thym du jardin. On s'éloigne d'un pas. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. On écoute le silence une seconde. Noé est assis. On se serre un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15443,6 +15891,11 @@
         <v>12</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15461,7 +15914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15478,6 +15931,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-EMO-011.xlsx
+++ b/stories/arbres/TREE-EMO-011.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|À la maison, le jeu devient trop fort. Trop de voix. Trop près. Noé sent que c'est trop. Maman est dans le couloir. Papa plie du linge. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1681,6 +1688,7 @@
           <t>narrateur|La pomme roule trop vite entre les mains. C'est trop. C'est une pomme. Le sable est un peu frais. Noé s'approche, sans courir. Papa n'est pas loin. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1864,6 +1872,7 @@
           <t>narrateur|C'est trop. Que dit-on ? Avec une pomme.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2035,6 +2044,7 @@
           <t>narrateur|Oui. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. Noé retient le geste. Il respire.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2226,6 +2236,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2393,6 +2404,7 @@
           <t>narrateur|Noé a choisi la cuisine, après une pomme. Un nuage passe devant le soleil. Près de la cuisine, Noé prend le temps. Pas de course. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2584,6 +2596,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2751,6 +2764,7 @@
           <t>narrateur|Noé rejoint les cubes, après une pomme et la cuisine. La tasse est encore tiède. On dit merci. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. On laisse les cubes à sa place. Noé est près de maman. Le soleil est encore là.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2918,6 +2932,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3085,6 +3100,7 @@
           <t>narrateur|Noé rejoint le livre, après une pomme et la cuisine. Le parquet craque un tout petit peu. On écoute jusqu'au bout. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. On écoute le silence une seconde. Noé est assis. On gardu geste.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3252,6 +3268,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3420,6 +3437,7 @@
 maman|Je t'ai entendu. Papa aussi. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3587,6 +3605,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3754,6 +3773,7 @@
           <t>narrateur|Noé a choisi le jardin, après une pomme. Ça sent le savon de maman. Noé range un peu autour du jardin. Il respire. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3945,6 +3965,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4112,6 +4133,7 @@
           <t>narrateur|Noé rejoint les cubes, après une pomme et le jardin. Un gravier roule sous une semelle. On pose les fesses sur une chaise. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. On laisse les cubes à sa place. Noé est près de maman. On respire.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4279,6 +4301,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4446,6 +4469,7 @@
           <t>narrateur|Noé rejoint le livre, après une pomme et le jardin. La fenêtre tremble un tout petit peu. On sourit un peu. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. On écoute le silence une seconde. Noé est assis. Merci, et au dodo bientôt.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4613,6 +4637,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4782,6 +4807,7 @@
 narrateur|Le jeu peut recommencer.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4949,6 +4975,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5116,6 +5143,7 @@
           <t>narrateur|Noé a choisi la chambre, après une pomme. Le lait est tiède. La chambre reste à sa place. Noé aussi. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5307,6 +5335,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5474,6 +5503,7 @@
           <t>narrateur|Noé rejoint les cubes, après une pomme et la chambre. Un pigeon roucoule. On essuie une miette. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. Noé serre la main de maman, tout doux. On se serre un peu.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5641,6 +5671,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5808,6 +5839,7 @@
           <t>narrateur|Noé rejoint le livre, après une pomme et la chambre. La cuillère tinte. On referme un livre. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. Noé nomme encore le mot, tout bas. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5975,6 +6007,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6142,6 +6175,7 @@
           <t>narrateur|Noé rejoint la dînette, après une pomme et la chambre. Le ballon est un peu poudreux. On pose un jouet à sa place. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. Noé pose la dînette et va vers maman. La journée continue, tout doux.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6309,6 +6343,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6476,6 +6511,7 @@
           <t>narrateur|Le yaourt manque de tomber. C'est trop. Noé s'occupe de un yaourt. Le soleil chauffe un peu le nez. Maman sourit. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6659,6 +6695,7 @@
           <t>narrateur|C'est trop. Que dit-on ? Avec un yaourt.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6830,6 +6867,7 @@
           <t>narrateur|Oui. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. Noé répète le mot. Maman hoche la tête.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7021,6 +7059,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7188,6 +7227,7 @@
           <t>narrateur|Noé a choisi la cuisine, après un yaourt. Le train souffle au loin. On continue avec la cuisine. Noé gardu geste sûr. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7379,6 +7419,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7546,6 +7587,7 @@
           <t>narrateur|Noé rejoint les cubes, après un yaourt et la cuisine. Une goutte de pluie sèche déjà. On marche tout doucement. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. On écoute le silence une seconde. Noé est assis. On se dit à plus tard.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7713,6 +7755,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7882,6 +7925,7 @@
 narrateur|Le soleil est encore là.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8049,6 +8093,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8216,6 +8261,7 @@
           <t>narrateur|Noé rejoint la dînette, après un yaourt et la cuisine. Ça sent le savon des mains. On ouvre les mains, loin de l'autre. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. On laisse la dînette à sa place. Noé est près de maman. On gardu geste.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8383,6 +8429,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8550,6 +8597,7 @@
           <t>narrateur|Noé a choisi le jardin, après un yaourt. Le pain croustille. Près du jardin, Noé prend le temps. Pas de course. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8741,6 +8789,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8908,6 +8957,7 @@
           <t>narrateur|Noé rejoint les cubes, après un yaourt et le jardin. Une feuille tourne et tombe. On s'assoit près de l'adulte. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. On écoute le silence une seconde. Noé est assis. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9075,6 +9125,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9242,6 +9293,7 @@
           <t>narrateur|Noé rejoint le livre, après un yaourt et le jardin. L'eau fait un tout petit bruit. On nomme ce qu'on sent. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. Noé pose le livre et va vers maman. On respire.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9409,6 +9461,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9576,6 +9629,7 @@
           <t>narrateur|Noé rejoint la dînette, après un yaourt et le jardin. Le soleil chauffe un peu le nez. On reprend le jeu, plus calme. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. Noé serre la main de maman, tout doux. Merci, et au dodo bientôt.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9743,6 +9797,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9910,6 +9965,7 @@
           <t>narrateur|Noé a choisi la chambre, après un yaourt. Le coussin est moelleux. Près de la chambre, Noé prend le temps. Pas de course. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10101,6 +10157,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10268,6 +10325,7 @@
           <t>narrateur|Noé rejoint les cubes, après un yaourt et la chambre. Une plume vole. On range les chaussures. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. Noé nomme encore le mot, tout bas. Le jeu peut recommencer.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10435,6 +10493,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10602,6 +10661,7 @@
           <t>narrateur|Noé rejoint le livre, après un yaourt et la chambre. Le pain croustille. On met le doudou près de soi. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. Noé pose le livre et va vers maman. On se serre un peu.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10769,6 +10829,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10936,6 +10997,7 @@
           <t>narrateur|Noé rejoint la dînette, après un yaourt et la chambre. La laine du doudou est douce. On écoute le cœur, tout doux. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. Noé serre la main de maman, tout doux. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11103,6 +11165,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11270,6 +11333,7 @@
           <t>narrateur|Le pain passe trop près du visage. C'est trop. Voilà un morceau de pain. Un coq chante une fois. Noé pose les pieds par terre, près de maman. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11453,6 +11517,7 @@
           <t>narrateur|C'est trop. Que dit-on ? Avec un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11624,6 +11689,7 @@
           <t>narrateur|Oui. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. Noé pose les pieds par terre. On continue, tout calme.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11815,6 +11881,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11982,6 +12049,7 @@
           <t>narrateur|Noé a choisi la cuisine, après un morceau de pain. La tasse est encore tiède. La cuisine est là. Noé pose les mains à vue, loin de l'autre. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12173,6 +12241,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12340,6 +12409,7 @@
           <t>narrateur|Noé rejoint les cubes, après un morceau de pain et la cuisine. Un galet est lisse dans la main. On secoue les mains, loin. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. Noé nomme encore le mot, tout bas. La journée continue, tout doux.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12507,6 +12577,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12674,6 +12745,7 @@
           <t>narrateur|Noé rejoint le livre, après un morceau de pain et la cuisine. Le train souffle au loin. On pose le sac. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. Noé serre la main de maman, tout doux. On se dit à plus tard.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12841,6 +12913,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13008,6 +13081,7 @@
           <t>narrateur|Noé rejoint la dînette, après un morceau de pain et la cuisine. Une vache meugle, loin. On dit le mot de l'émotion. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. Noé range la dînette un instant. Puis il reprend, calme. Le soleil est encore là.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13175,6 +13249,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13342,6 +13417,7 @@
           <t>narrateur|Noé a choisi le jardin, après un morceau de pain. Ça sent le pain encore chaud. Noé attend près du jardin. Il ne prend pas de force. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13533,6 +13609,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13701,6 +13778,7 @@
 maman|Je t'ai entendu. Papa aussi. On gardu geste.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13868,6 +13946,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14035,6 +14114,7 @@
           <t>narrateur|Noé rejoint le livre, après un morceau de pain et le jardin. Le bois de la table est lisse. On attend la réponse. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. On écoute le silence une seconde. Noé est assis. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14202,6 +14282,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14369,6 +14450,7 @@
           <t>narrateur|Noé rejoint la dînette, après un morceau de pain et le jardin. Une goutte tombe dans l'évier. On propose une autre idée. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. Noé serre la main de maman, tout doux. On respire.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14536,6 +14618,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14703,6 +14786,7 @@
           <t>narrateur|Noé a choisi la chambre, après un morceau de pain. Un nuage passe devant le soleil. On continue avec la chambre. Noé gardu geste sûr. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14894,6 +14978,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15061,6 +15146,7 @@
           <t>narrateur|Noé rejoint les cubes, après un morceau de pain et la chambre. Le toboggan est un peu froid. On va vers papa ou maman. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. Noé nomme encore le mot, tout bas. Merci, et au dodo bientôt.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15228,6 +15314,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15395,6 +15482,7 @@
           <t>narrateur|Noé rejoint le livre, après un morceau de pain et la chambre. La clochette de la porte tinte. On dit stop, tout clair. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. Noé boit une gorgée. Il se sent plus léger. Le jeu peut recommencer.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15562,6 +15650,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15729,6 +15818,7 @@
           <t>narrateur|Noé rejoint la dînette, après un morceau de pain et la chambre. Ça sent le thym du jardin. On s'éloigne d'un pas. C'est trop. Noé dit stop. Il s'éloigne. Il va vers un adulte, vers maman. On écoute le silence une seconde. Noé est assis. On se serre un peu.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15896,6 +15986,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15914,7 +16005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15938,6 +16029,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15952,7 +16057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16139,6 +16244,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
